--- a/simulations/BAU_nitrous_oxide/economics_BAU.xlsx
+++ b/simulations/BAU_nitrous_oxide/economics_BAU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\BAU_nitrous_oxide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6861B6-4102-4B6A-B019-BF378C26CC99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A62181B-018E-4671-AF65-BAF71D7415B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -1099,7 +1099,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1234,6 +1234,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3312,7 +3315,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:K18"/>
+  <dimension ref="B2:M18"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="11"/>
@@ -3327,10 +3330,10 @@
     <col min="12" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>23</v>
       </c>
@@ -3356,7 +3359,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
         <v>101</v>
       </c>
@@ -3375,8 +3378,16 @@
         <f>J4*596.2/550.8*596.2/550.8*596.2/550.8</f>
         <v>923.47874215069317</v>
       </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="50">
+        <f>J4/1000</f>
+        <v>0.72816999999999998</v>
+      </c>
+      <c r="M4" s="50">
+        <f>K4/1000</f>
+        <v>0.92347874215069314</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>98</v>
       </c>
@@ -3403,8 +3414,16 @@
       <c r="K5" s="41">
         <v>925.28</v>
       </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="50">
+        <f>J5/1000</f>
+        <v>1.3660300000000001</v>
+      </c>
+      <c r="M5" s="50">
+        <f>K5/1000</f>
+        <v>0.92527999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>99</v>
       </c>
@@ -3414,7 +3433,7 @@
       <c r="D6" s="23">
         <v>33.362867039999998</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="41">
         <v>728.17</v>
       </c>
       <c r="F6" s="41">
@@ -3427,8 +3446,10 @@
       </c>
       <c r="J6" s="49"/>
       <c r="K6" s="49"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="40" t="s">
         <v>102</v>
       </c>
@@ -3438,7 +3459,7 @@
       <c r="D7" s="23">
         <v>33.362867039999998</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="41">
         <v>1366.03</v>
       </c>
       <c r="F7" s="41">
@@ -3449,8 +3470,10 @@
         <f>F7/Summary!$C$23</f>
         <v>1.2217818076065263</v>
       </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="51" t="s">
         <v>103</v>
       </c>
@@ -3464,8 +3487,10 @@
       </c>
       <c r="J8" s="57"/>
       <c r="K8" s="57"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
@@ -3496,8 +3521,10 @@
       <c r="K9" s="46" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>132</v>
       </c>
@@ -3528,8 +3555,16 @@
       <c r="K10" s="41">
         <v>1024.96</v>
       </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="50">
+        <f>J10/1000</f>
+        <v>0.66849000000000003</v>
+      </c>
+      <c r="M10" s="50">
+        <f>K10/1000</f>
+        <v>1.0249600000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>25</v>
       </c>
@@ -3539,7 +3574,7 @@
       <c r="D11" s="30">
         <v>20416.40624796</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="58">
         <f>69.6/1000*C18/C17</f>
         <v>9.3487407407407408E-2</v>
       </c>
@@ -3560,8 +3595,16 @@
       <c r="K11" s="41">
         <v>1742</v>
       </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="50">
+        <f>J11/1000</f>
+        <v>0.78965999999999992</v>
+      </c>
+      <c r="M11" s="50">
+        <f>K11/1000</f>
+        <v>1.742</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>105</v>
       </c>
@@ -3574,8 +3617,10 @@
         <f>(F5+F6+F9+F10+F11)/1000000*8000</f>
         <v>212.16089639476388</v>
       </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="35" t="s">
         <v>106</v>
       </c>
@@ -3593,8 +3638,10 @@
       </c>
       <c r="J13" s="57"/>
       <c r="K13" s="57"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -3609,8 +3656,10 @@
       <c r="K14" s="46" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
         <v>84</v>
       </c>
@@ -3628,8 +3677,16 @@
       <c r="K15" s="41">
         <v>658.84</v>
       </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="50">
+        <f>J15/1000</f>
+        <v>0.78495693082808915</v>
+      </c>
+      <c r="M15" s="50">
+        <f>K15/1000</f>
+        <v>0.65883999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>83</v>
       </c>
@@ -3645,6 +3702,14 @@
       </c>
       <c r="K16" s="41">
         <v>1191.73</v>
+      </c>
+      <c r="L16" s="50">
+        <f>J16/1000</f>
+        <v>1.062000553473297</v>
+      </c>
+      <c r="M16" s="50">
+        <f>K16/1000</f>
+        <v>1.19173</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">

--- a/simulations/BAU_nitrous_oxide/economics_BAU.xlsx
+++ b/simulations/BAU_nitrous_oxide/economics_BAU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\BAU_nitrous_oxide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A62181B-018E-4671-AF65-BAF71D7415B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C693F4B-2B60-4A14-B8BF-E268358DFF3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -1099,7 +1099,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1215,6 +1215,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1236,7 +1239,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1707,16 +1710,16 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="53"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
       <c r="J13" s="32" t="s">
         <v>46</v>
       </c>
@@ -2084,16 +2087,16 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="53"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
@@ -2123,16 +2126,16 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="53"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
@@ -2679,16 +2682,16 @@
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="56"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="57"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
@@ -2775,16 +2778,16 @@
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="51" t="s">
+      <c r="A43" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="52"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="53"/>
+      <c r="B43" s="53"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="54"/>
       <c r="O43" s="42"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -3124,11 +3127,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="57">
+      <c r="A3" s="58">
         <v>2022</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
@@ -3142,11 +3145,11 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -3185,19 +3188,19 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
-      <c r="B9" s="53"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="17">
         <f>SUM(C6:C8)</f>
         <v>7.3406250000000002</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
@@ -3212,19 +3215,19 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="28">
         <f>C11</f>
         <v>4.6803316079964707</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="54"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -3251,19 +3254,19 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="28">
         <f>SUM(C14:C15)</f>
         <v>11.869909188794647</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
@@ -3278,18 +3281,18 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="57"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="17">
         <f>C18</f>
         <v>2.555461057966073</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="53"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="17">
         <f>C9+C12+C16+C19</f>
         <v>26.446326854757192</v>
@@ -3360,13 +3363,13 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
       <c r="G4" s="1"/>
       <c r="I4" s="48" t="s">
         <v>134</v>
@@ -3374,9 +3377,9 @@
       <c r="J4" s="41">
         <v>728.17</v>
       </c>
-      <c r="K4" s="41">
-        <f>J4*596.2/550.8*596.2/550.8*596.2/550.8</f>
-        <v>923.47874215069317</v>
+      <c r="K4" s="59">
+        <f>J4*596.2/550.8*596.2/550.8*596.2/550.8/(1+0.02)^30</f>
+        <v>509.82573013318409</v>
       </c>
       <c r="L4" s="50">
         <f>J4/1000</f>
@@ -3384,7 +3387,7 @@
       </c>
       <c r="M4" s="50">
         <f>K4/1000</f>
-        <v>0.92347874215069314</v>
+        <v>0.50982573013318411</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
@@ -3474,19 +3477,19 @@
       <c r="M7" s="50"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
       <c r="G8" s="50"/>
-      <c r="I8" s="57">
+      <c r="I8" s="58">
         <v>2022</v>
       </c>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
     </row>
@@ -3574,7 +3577,7 @@
       <c r="D11" s="30">
         <v>20416.40624796</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="51">
         <f>69.6/1000*C18/C17</f>
         <v>9.3487407407407408E-2</v>
       </c>
@@ -3633,11 +3636,11 @@
         <f>(F5+F7+F9+F10+F11)/1000000*8000</f>
         <v>382.40760335583906</v>
       </c>
-      <c r="I13" s="57">
+      <c r="I13" s="58">
         <v>2050</v>
       </c>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
       <c r="L13" s="50"/>
       <c r="M13" s="50"/>
     </row>
@@ -3670,16 +3673,16 @@
       <c r="I15" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="59">
         <f>K4*0.85</f>
-        <v>784.95693082808918</v>
+        <v>433.35187061320647</v>
       </c>
       <c r="K15" s="41">
         <v>658.84</v>
       </c>
       <c r="L15" s="50">
         <f>J15/1000</f>
-        <v>0.78495693082808915</v>
+        <v>0.43335187061320646</v>
       </c>
       <c r="M15" s="50">
         <f>K15/1000</f>
@@ -3696,16 +3699,16 @@
       <c r="I16" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="59">
         <f>K4*1.15</f>
-        <v>1062.000553473297</v>
+        <v>586.29958965316166</v>
       </c>
       <c r="K16" s="41">
         <v>1191.73</v>
       </c>
       <c r="L16" s="50">
         <f>J16/1000</f>
-        <v>1.062000553473297</v>
+        <v>0.58629958965316165</v>
       </c>
       <c r="M16" s="50">
         <f>K16/1000</f>
@@ -3753,14 +3756,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="E2" s="57" t="s">
+      <c r="C2" s="58"/>
+      <c r="E2" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="57"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
